--- a/backend/assets/templates/tracker-10-medidas-template.xlsx
+++ b/backend/assets/templates/tracker-10-medidas-template.xlsx
@@ -599,7 +599,7 @@
       <c r="F8" s="7" t="n"/>
       <c r="G8" s="6" t="inlineStr">
         <is>
-          <t>Análise de risco anual documentada com metodologia (ISO 27005 ou CNCS). Inventário de ativos críticos atualizado. PSI aprovada e assinada pela gestão. Ferramentas sugeridas: Registo de Riscos (gerado pela plataforma) + CNCS Risk Framework.</t>
+          <t>Análise de risco anual documentada com metodologia (ISO 27005 ou CNCS). Inventário de ativos críticos atualizado. PSI aprovada e assinada pela gestão. Exemplos de referência (entre outras): Registo de Riscos (gerado pela plataforma); CNCS Risk Framework.</t>
         </is>
       </c>
       <c r="H8" s="7" t="n"/>
@@ -627,7 +627,7 @@
       <c r="F9" s="7" t="n"/>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>IRP documentado e testado com tabletop semestral. EDR em todos os endpoints. Log de incidentes atualizado. Processo de notificação ao CNCS (24h/72h/1 mês) testado. Ferramentas sugeridas: EDR (Microsoft Defender / Sophos Intercept X); IRP gerado pela plataforma.</t>
+          <t>IRP documentado e testado com tabletop semestral. EDR em todos os endpoints. Log de incidentes atualizado. Processo de notificação ao CNCS (24h/72h/1 mês) testado. Exemplos de soluções (entre outras, sem endosso): EDR (Microsoft Defender, Sophos Intercept X, CrowdStrike ou equivalente); IRP gerado pela plataforma.</t>
         </is>
       </c>
       <c r="H9" s="7" t="n"/>
@@ -655,7 +655,7 @@
       <c r="F10" s="7" t="n"/>
       <c r="G10" s="6" t="inlineStr">
         <is>
-          <t>Backup 3-2-1 com imutabilidade configurado e testado trimestralmente. BCP com RTO e RPO definidos e aprovados. DRP com procedimentos de restauro documentados. Ferramentas sugeridas: Veeam Backup / Azure Backup / Acronis; NAS local + Cloud.</t>
+          <t>Backup 3-2-1 com imutabilidade configurado e testado trimestralmente. BCP com RTO e RPO definidos e aprovados. DRP com procedimentos de restauro documentados. Exemplos de soluções (entre outras, sem endosso): Veeam Backup, Azure Backup, Acronis ou equivalente; armazenamento local (NAS) combinado com cloud.</t>
         </is>
       </c>
       <c r="H10" s="7" t="n"/>
@@ -711,7 +711,7 @@
       <c r="F12" s="7" t="n"/>
       <c r="G12" s="6" t="inlineStr">
         <is>
-          <t>Critérios de segurança formais na aquisição de software/hardware. Processo de gestão de patches com prazos por CVSS (Crítico ≤48h, Alto ≤1 semana). Inventário de sistemas em fim de vida (EOL) com plano de migração. Práticas de desenvolvimento seguro (SAST, revisão de código) se a empresa desenvolve software. Subscrição de alertas CVE (CERT.PT, CISA) e scan de vulnerabilidades trimestral — inclui a divulgação e o tratamento de vulnerabilidades (Art. 21.º/2/e). Ferramentas sugeridas: Windows Update for Business/WSUS; CERT.PT alerts; Nessus Essentials / Qualys FreeScan.</t>
+          <t>Critérios de segurança formais na aquisição de software/hardware. Processo de gestão de patches com prazos por CVSS (Crítico ≤48h, Alto ≤1 semana). Inventário de sistemas em fim de vida (EOL) com plano de migração. Práticas de desenvolvimento seguro (SAST, revisão de código) se a empresa desenvolve software. Subscrição de alertas CVE (CERT.PT, CISA) e scan de vulnerabilidades trimestral — inclui a divulgação e o tratamento de vulnerabilidades (Art. 21.º/2/e). Exemplos de soluções (entre outras, sem endosso): gestão de patches (Windows Update for Business/WSUS, Chocolatey, Ansible ou equivalente); CERT.PT alerts (gratuito); scan de vulnerabilidades (Nessus Essentials, Qualys FreeScan, OpenVAS ou equivalente).</t>
         </is>
       </c>
       <c r="H12" s="7" t="n"/>
@@ -739,7 +739,7 @@
       <c r="F13" s="7" t="n"/>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>Avaliações periódicas da eficácia das medidas (auditoria interna/externa). Testes de vulnerabilidade e scans regulares nos sistemas expostos à internet (a plataforma CISPLAN automatiza esta análise). Logs de segurança retidos ≥12 meses, com monitorização ativa de alertas críticos (SIEM). Resultados documentados e usados para um ciclo de melhoria contínua com responsáveis e prazos. Ferramentas sugeridas: Microsoft Sentinel (SIEM) ou equivalente; scan de vulnerabilidades da própria plataforma.</t>
+          <t>Avaliações periódicas da eficácia das medidas (auditoria interna/externa). Testes de vulnerabilidade e scans regulares nos sistemas expostos à internet (a plataforma CISPLAN automatiza esta análise). Logs de segurança retidos ≥12 meses, com monitorização ativa de alertas críticos (SIEM). Resultados documentados e usados para um ciclo de melhoria contínua com responsáveis e prazos. Exemplos de soluções (entre outras, sem endosso): SIEM/monitorização (Microsoft Sentinel, Wazuh, Elastic Security ou equivalente); scan de vulnerabilidades da própria plataforma.</t>
         </is>
       </c>
       <c r="H13" s="7" t="n"/>
@@ -767,7 +767,7 @@
       <c r="F14" s="7" t="n"/>
       <c r="G14" s="6" t="inlineStr">
         <is>
-          <t>Formação anual de cibersegurança para 100% dos colaboradores, com lista de presenças. Formação técnica especializada adicional para TI/CISO. Política de Uso Aceitável (AUP) comunicada e assinada. Simulações de phishing trimestrais com resultado documentado. Meta: taxa de cliques em phishing &lt; 5%. Ferramentas sugeridas: KnowBe4 / Proofpoint Security Awareness / C-Academy (CNCS, gratuito).</t>
+          <t>Formação anual de cibersegurança para 100% dos colaboradores, com lista de presenças. Formação técnica especializada adicional para TI/CISO. Política de Uso Aceitável (AUP) comunicada e assinada. Simulações de phishing trimestrais com resultado documentado. Meta: taxa de cliques em phishing &lt; 5%. Exemplos de soluções (entre outras, sem endosso): KnowBe4, Proofpoint Security Awareness, ou C-Academy (CNCS, gratuito).</t>
         </is>
       </c>
       <c r="H14" s="7" t="n"/>
@@ -795,7 +795,7 @@
       <c r="F15" s="7" t="n"/>
       <c r="G15" s="6" t="inlineStr">
         <is>
-          <t>Encriptação de dados em repouso ativa (BitLocker/FileVault, encriptação de base de dados). Todos os dados em trânsito encriptados (HTTPS em todos os sites, TLS, VPN para acesso remoto). Política de gestão de chaves criptográficas, com responsáveis e rotação definida. Ferramentas sugeridas: Microsoft Intune (BitLocker); certificados TLS (Let's Encrypt).</t>
+          <t>Encriptação de dados em repouso ativa (BitLocker/FileVault, encriptação de base de dados). Todos os dados em trânsito encriptados (HTTPS em todos os sites, TLS, VPN para acesso remoto). Política de gestão de chaves criptográficas, com responsáveis e rotação definida. Exemplos de soluções (entre outras, sem endosso): encriptação de disco nativa (BitLocker/FileVault, geríveis via Microsoft Intune, Jamf ou equivalente); certificados TLS (Let's Encrypt, gratuito, ou fornecedores comerciais).</t>
         </is>
       </c>
       <c r="H15" s="7" t="n"/>
@@ -823,7 +823,7 @@
       <c r="F16" s="7" t="n"/>
       <c r="G16" s="6" t="inlineStr">
         <is>
-          <t>Inventário atualizado de todos os ativos de TI (hardware, software, cloud) — não se pode proteger o que não se conhece. Princípio do menor privilégio implementado (cada colaborador só com os acessos necessários). Processo de onboarding/offboarding com revogação imediata de acessos à saída. Revisão periódica de permissões (semestral/anual). Contas de administrador geridas de forma especial (separadas, MFA obrigatório, auditoria de uso). Ferramentas sugeridas: Microsoft Entra ID (IAM/RBAC); revisão trimestral de acessos.</t>
+          <t>Inventário atualizado de todos os ativos de TI (hardware, software, cloud) — não se pode proteger o que não se conhece. Princípio do menor privilégio implementado (cada colaborador só com os acessos necessários). Processo de onboarding/offboarding com revogação imediata de acessos à saída. Revisão periódica de permissões (semestral/anual). Contas de administrador geridas de forma especial (separadas, MFA obrigatório, auditoria de uso). Exemplos de soluções (entre outras, sem endosso): gestão de identidade e acessos (Microsoft Entra ID, Okta, Google Workspace ou equivalente); revisão trimestral de acessos.</t>
         </is>
       </c>
       <c r="H16" s="7" t="n"/>
@@ -851,7 +851,7 @@
       <c r="F17" s="7" t="n"/>
       <c r="G17" s="6" t="inlineStr">
         <is>
-          <t>MFA ativo para 100% das contas: email corporativo, VPN/acesso remoto, contas de administrador, sistemas críticos. Contas de serviço/APIs com tokens ou certificados rotativos (não passwords estáticas partilhadas). Canais aprovados e seguros para comunicações sensíveis (não WhatsApp pessoal/SMS). PRIORIDADE MÁXIMA — maior ROI de qualquer medida NIS2. Ferramentas sugeridas: Microsoft Authenticator/Entra ID; Microsoft Intune (MDM); Cisco Duo.</t>
+          <t>MFA ativo para 100% das contas: email corporativo, VPN/acesso remoto, contas de administrador, sistemas críticos. Contas de serviço/APIs com tokens ou certificados rotativos (não passwords estáticas partilhadas). Canais aprovados e seguros para comunicações sensíveis (não WhatsApp pessoal/SMS). PRIORIDADE MÁXIMA — maior ROI de qualquer medida NIS2. Exemplos de soluções (entre outras, sem endosso): MFA (Microsoft Authenticator/Entra ID, Cisco Duo, Google Authenticator ou equivalente); gestão de dispositivos móveis (Microsoft Intune, Jamf ou equivalente).</t>
         </is>
       </c>
       <c r="H17" s="7" t="n"/>
@@ -870,7 +870,7 @@
   </mergeCells>
   <dataValidations count="1">
     <dataValidation sqref="D8:D17" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"Conforme,Parcial,Em falta"</formula1>
+      <formula1>"Conforme,Parcial,Em falta,Não avaliado"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1278,10 +1278,21 @@
         <v/>
       </c>
     </row>
+    <row r="10">
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Medidas NÃO AVALIADAS (sem respostas aplicáveis) ⚪</t>
+        </is>
+      </c>
+      <c r="C10">
+        <f>COUNTIF('📊 TRACKER 10 MEDIDAS'!D8:D17,"Não avaliado")</f>
+        <v/>
+      </c>
+    </row>
     <row r="11">
       <c r="B11" s="10" t="inlineStr">
         <is>
-          <t>ℹ️  As contagens por estado são calculadas automaticamente a partir da coluna Estado do separador '📊 TRACKER 10 MEDIDAS'. O Score Global reflete o resultado do questionário de autoavaliação NIS2 — o mesmo valor usado no Relatório Executivo para a Gestão.</t>
+          <t>ℹ️  As contagens por estado são calculadas automaticamente a partir da coluna Estado do separador '📊 TRACKER 10 MEDIDAS'. "Não avaliado" significa que a medida não teve nenhuma resposta aplicável no questionário (tudo N/A) — não é o mesmo que "Em falta" (medida avaliada e reprovada). O Score Global reflete o resultado do questionário de autoavaliação NIS2 — o mesmo valor usado no Relatório Executivo para a Gestão.</t>
         </is>
       </c>
     </row>
